--- a/data/Mar/18-03-2026/NGAY 18-3.xlsx
+++ b/data/Mar/18-03-2026/NGAY 18-3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\18-03-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\18-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F604087-F968-4F71-8087-748ACECA211D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE95C9FA-7173-46C8-A778-D9628FA1BB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EAF8504-9B99-4CC8-A026-1F30ACB00849}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$Q$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -340,13 +340,49 @@
   </si>
   <si>
     <t>NGAY 18-3</t>
+  </si>
+  <si>
+    <t>PUNLORK</t>
+  </si>
+  <si>
+    <t>Xe Phy Phy</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>thu hộ shop</t>
+  </si>
+  <si>
+    <t>sha sha</t>
+  </si>
+  <si>
+    <t>HD002320</t>
+  </si>
+  <si>
+    <t>532/3/6 kinh duong vuong</t>
+  </si>
+  <si>
+    <t>binh tan</t>
+  </si>
+  <si>
+    <t>16-03-2026</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>xx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,6 +403,21 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -414,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -425,16 +476,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFD3D3D3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -445,6 +535,37 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AA0806E6-9C59-4025-B8D5-AA077A425D2A}" name="Table2" displayName="Table2" ref="A2:Q22" totalsRowShown="0" headerRowDxfId="3">
+  <autoFilter ref="A2:Q22" xr:uid="{21EF95A6-1E82-4AC8-A681-DBF8AEA4F795}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q21">
+    <sortCondition ref="J2:J21"/>
+  </sortState>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{D9485E50-1BFF-4A58-A832-44B337C89C0D}" name="Tình trạng TT"/>
+    <tableColumn id="2" xr3:uid="{5C95BA54-2804-4307-8695-1792E0EF4E78}" name="SHOP"/>
+    <tableColumn id="3" xr3:uid="{64B1B5CD-0B59-4E7D-BB4B-0797233375E6}" name="TÊN KH"/>
+    <tableColumn id="4" xr3:uid="{640D6B6F-C7B0-4B1F-8F8B-5BACFD8CA57E}" name="MÃ"/>
+    <tableColumn id="5" xr3:uid="{3D8919AD-4F8E-42C0-9ACB-2EDA6A5F70B9}" name="ĐỊA CHỈ"/>
+    <tableColumn id="6" xr3:uid="{4A8527BB-CE9F-46EB-B350-7E3518D16A1D}" name="QUẬN"/>
+    <tableColumn id="7" xr3:uid="{7A047805-0921-49A3-9F48-338B0AD7DAF7}" name="TIỀN THU" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{8AB1C2BD-B28C-442F-A4EE-53F3494F0652}" name="TIỀN SHIP" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{AB48E7F8-D8C7-4B4B-AB86-7C25DA9BD5EE}" name="TIỀN HÀNG" dataDxfId="0">
+      <calculatedColumnFormula>G3-H3</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{D0AEBC5B-E77F-4FD6-8924-1E1D765208B5}" name="NGƯỜI ĐI"/>
+    <tableColumn id="11" xr3:uid="{7C52E21C-863F-4206-B82D-9749A3DF5A28}" name="NGƯỜI LẤY"/>
+    <tableColumn id="12" xr3:uid="{87570B00-DDD4-463E-835E-6436C9C85FFC}" name="NGÀY LẤY"/>
+    <tableColumn id="13" xr3:uid="{226B3CBF-E4F4-45F2-92C6-D4FBBE6EB22E}" name="GHI CHÚ"/>
+    <tableColumn id="14" xr3:uid="{9FAEC375-5DCB-4AD2-8A4E-54E8259BC64B}" name="ỨNG TIỀN"/>
+    <tableColumn id="15" xr3:uid="{30B7D3C9-F7C6-45D2-9EE3-291B0155D98A}" name="HÀNG TỒN"/>
+    <tableColumn id="16" xr3:uid="{220C2C6D-DD14-4E7D-9DE7-CCE8AE482351}" name="FAIL"/>
+    <tableColumn id="17" xr3:uid="{E16C48B9-FCC8-41AD-B59A-31F97DAD7D1D}" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,24 +865,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EF95A6-1E82-4AC8-A681-DBF8AEA4F795}">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="55.140625" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" customWidth="1"/>
     <col min="16" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -821,6 +944,9 @@
       <c r="P2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="Q2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -881,10 +1007,10 @@
         <v>7</v>
       </c>
       <c r="G4" s="2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="H4" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <f>G4-H4</f>
@@ -1105,39 +1231,42 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>68</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
+        <v>102</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
       </c>
       <c r="G10" s="2">
-        <v>870</v>
+        <v>1860</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
         <f>G10-H10</f>
-        <v>840</v>
+        <v>1830</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="K10" t="s">
         <v>18</v>
       </c>
       <c r="L10" t="s">
         <v>48</v>
+      </c>
+      <c r="M10" t="s">
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>1</v>
@@ -1148,26 +1277,26 @@
         <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" t="s">
-        <v>17</v>
+        <v>69</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
       </c>
       <c r="G11" s="2">
-        <v>1630</v>
+        <v>870</v>
       </c>
       <c r="H11" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2">
         <f>G11-H11</f>
-        <v>1610</v>
+        <v>840</v>
       </c>
       <c r="J11" t="s">
         <v>18</v>
@@ -1187,26 +1316,26 @@
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="2">
-        <v>0</v>
+        <v>1630</v>
       </c>
       <c r="H12" s="2">
         <v>20</v>
       </c>
       <c r="I12" s="2">
-        <f>-H12</f>
-        <v>-20</v>
+        <f>G12-H12</f>
+        <v>1610</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
@@ -1226,26 +1355,26 @@
         <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
         <v>17</v>
       </c>
       <c r="G13" s="2">
-        <v>810</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2">
         <v>20</v>
       </c>
       <c r="I13" s="2">
-        <f>G13-H13</f>
-        <v>790</v>
+        <f>-H13</f>
+        <v>-20</v>
       </c>
       <c r="J13" t="s">
         <v>18</v>
@@ -1261,30 +1390,30 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>40</v>
-      </c>
       <c r="B14" t="s">
         <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="2">
-        <v>30</v>
+        <v>810</v>
       </c>
       <c r="H14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
         <f>G14-H14</f>
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="J14" t="s">
         <v>18</v>
@@ -1307,13 +1436,13 @@
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" s="2">
         <v>30</v>
@@ -1346,23 +1475,23 @@
         <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <f>-H16</f>
-        <v>-30</v>
+        <f>G16-H16</f>
+        <v>0</v>
       </c>
       <c r="J16" t="s">
         <v>18</v>
@@ -1378,33 +1507,33 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
       <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F17" s="2">
-        <v>10</v>
+        <v>84</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
       </c>
       <c r="G17" s="2">
-        <v>1455</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2">
-        <f>G17-H17</f>
-        <v>1430</v>
+        <f>-H17</f>
+        <v>-30</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
         <v>18</v>
@@ -1421,26 +1550,26 @@
         <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" t="s">
-        <v>91</v>
+        <v>87</v>
+      </c>
+      <c r="F18" s="2">
+        <v>10</v>
       </c>
       <c r="G18" s="2">
-        <v>660</v>
+        <v>1455</v>
       </c>
       <c r="H18" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" s="2">
         <f>G18-H18</f>
-        <v>640</v>
+        <v>1430</v>
       </c>
       <c r="J18" t="s">
         <v>39</v>
@@ -1460,26 +1589,26 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F19" t="s">
         <v>91</v>
       </c>
       <c r="G19" s="2">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="H19" s="2">
         <v>20</v>
       </c>
       <c r="I19" s="2">
         <f>G19-H19</f>
-        <v>580</v>
+        <v>640</v>
       </c>
       <c r="J19" t="s">
         <v>39</v>
@@ -1499,26 +1628,26 @@
         <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2">
-        <v>875</v>
+        <v>600</v>
       </c>
       <c r="H20" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I20" s="2">
         <f>G20-H20</f>
-        <v>850</v>
+        <v>580</v>
       </c>
       <c r="J20" t="s">
         <v>39</v>
@@ -1533,394 +1662,490 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D22" s="3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2">
+        <v>875</v>
+      </c>
+      <c r="H21" s="2">
+        <v>25</v>
+      </c>
+      <c r="I21" s="2">
+        <f>G21-H21</f>
+        <v>850</v>
+      </c>
+      <c r="J21" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="18">
+        <v>750</v>
+      </c>
+      <c r="H22" s="18">
+        <v>30</v>
+      </c>
+      <c r="I22" s="18">
+        <v>720</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="O22" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D23" s="3">
         <f>COUNTA(D3:D20)</f>
-        <v>15</v>
-      </c>
-      <c r="G22" s="3">
-        <f t="shared" ref="G22:Q22" si="0">SUBTOTAL(9,G3:G20)</f>
-        <v>10165</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="0"/>
-        <v>475</v>
-      </c>
-      <c r="I22" s="3">
-        <f t="shared" si="0"/>
-        <v>9690</v>
-      </c>
-      <c r="J22" s="3">
-        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G23" s="15">
+        <f>SUBTOTAL(9,G3:G22)</f>
+        <v>12745</v>
+      </c>
+      <c r="H23" s="15">
+        <f>SUBTOTAL(9,H3:H22)</f>
+        <v>505</v>
+      </c>
+      <c r="I23" s="15">
+        <f>SUBTOTAL(9,I3:I22)</f>
+        <v>12240</v>
+      </c>
+      <c r="J23" s="3">
+        <f>SUBTOTAL(9,J3:J20)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="3">
-        <f t="shared" si="0"/>
+      <c r="K23" s="3">
+        <f>SUBTOTAL(9,K3:K20)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <f t="shared" si="0"/>
+      <c r="L23" s="3">
+        <f>SUBTOTAL(9,L3:L20)</f>
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <f t="shared" si="0"/>
+      <c r="M23" s="3">
+        <f>SUBTOTAL(9,M3:M20)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="3">
-        <f t="shared" si="0"/>
+      <c r="N23" s="3">
+        <f>SUBTOTAL(9,N3:N20)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="3">
-        <f t="shared" si="0"/>
+      <c r="O23" s="3">
+        <f>SUBTOTAL(9,O3:O20)</f>
         <v>0</v>
       </c>
-      <c r="P22" s="3">
-        <f t="shared" si="0"/>
+      <c r="P23" s="3">
+        <f>SUBTOTAL(9,P3:P20)</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="H23">
+      <c r="Q23" s="15">
+        <f>SUBTOTAL(9,Q3:Q22)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H24">
         <f>-3*17</f>
         <v>-51</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
+        <v>-750</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H25">
         <f>-4*25</f>
         <v>-100</v>
       </c>
-      <c r="K24" s="5" t="s">
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="10"/>
+      <c r="E27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="L27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M24" s="5" t="s">
+      <c r="M27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B28" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="13">
-        <f>SUMIFS(I$3:I$20,B$3:B$20,A$24,L$3:L$20,A$25)</f>
-        <v>9690</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="6">
-        <f>SUMIFS(Q$3:Q$20,B$3:B$20,A$24,L$3:L$20,A$25)</f>
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="C28" s="16">
+        <f>SUMIFS(I$3:I$22,B$3:B$22,A$27,L$3:L$22,A$28)+I24</f>
+        <v>10770</v>
+      </c>
+      <c r="D28" s="11"/>
+      <c r="E28" s="6">
+        <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,L$3:L$22,A$28)</f>
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
         <v>24</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K28" t="s">
         <v>25</v>
       </c>
-      <c r="L25">
-        <f>SUMIFS(G$3:G$20,J$3:J$20,K$24)</f>
-        <v>3205</v>
-      </c>
-      <c r="M25">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$24)</f>
-        <v>7</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="L28">
+        <f>SUMIFS(G$3:G$22,J$3:J$22,K$27)</f>
+        <v>5035</v>
+      </c>
+      <c r="M28">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$27)</f>
+        <v>8</v>
+      </c>
+      <c r="O28" t="s">
         <v>98</v>
       </c>
-      <c r="P25">
-        <f>L30</f>
-        <v>3054</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="14">
-        <v>0</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="K26" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26">
-        <f>SUM(H23:H24)</f>
-        <v>-151</v>
-      </c>
-      <c r="M26">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$24)</f>
-        <v>7</v>
-      </c>
-      <c r="O26" t="s">
-        <v>39</v>
-      </c>
-      <c r="P26">
-        <f>L38</f>
-        <v>3520</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="14">
-        <f>-SUMIFS(I$3:I$20,B$3:B$20,A$24,P$3:P$20,"xx",N$3:N$20,"x")</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="7">
-        <f>SUMIFS(Q$3:Q$20,B$3:B$20,A$24,P$3:P$20,"xx",N$3:N$20,"x")</f>
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>28</v>
-      </c>
-      <c r="O27" t="s">
-        <v>18</v>
-      </c>
-      <c r="P27">
-        <f>L46</f>
-        <v>3191</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="12">
-        <f>SUBTOTAL(9,C25:C27)</f>
-        <v>9690</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28">
-        <f>E25</f>
-        <v>18</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" t="s">
-        <v>33</v>
-      </c>
       <c r="P28">
-        <f>-C32</f>
-        <v>-9690</v>
+        <f>L33</f>
+        <v>4134</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="12">
+        <v>0</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="K29" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29">
+        <f>SUM(H24:H25)</f>
+        <v>-151</v>
+      </c>
+      <c r="M29">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$27)</f>
+        <v>8</v>
+      </c>
+      <c r="O29" t="s">
+        <v>39</v>
+      </c>
+      <c r="P29">
+        <f>L41</f>
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="19">
+        <f>-SUMIFS(I$3:I$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
+        <v>-720</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="17">
+        <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
+        <v>1</v>
+      </c>
+      <c r="K30" t="s">
+        <v>28</v>
+      </c>
+      <c r="O30" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30">
+        <f>L49</f>
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="10">
+        <f>SUBTOTAL(9,C28:C30)</f>
+        <v>10050</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31">
+        <f>E28</f>
+        <v>19</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O31" t="s">
+        <v>33</v>
+      </c>
+      <c r="P31">
+        <f>-C35</f>
+        <v>-10050</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="K29" s="7" t="s">
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="K32" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="L32">
+        <v>-750</v>
+      </c>
+      <c r="O32" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="P29" s="4">
-        <f>SUBTOTAL(9,P25:P28)</f>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
+      <c r="P32" s="4">
+        <f>SUBTOTAL(9,P28:P31)</f>
+        <v>736</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="L30" s="9">
-        <f>SUBTOTAL(9,L25:L29)</f>
-        <v>3054</v>
-      </c>
-      <c r="M30" s="9">
-        <f>M25</f>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="L33" s="9">
+        <f>SUBTOTAL(9,L28:L32)</f>
+        <v>4134</v>
+      </c>
+      <c r="M33" s="9">
+        <f>M28</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="14">
+        <f>C31+C32+C33</f>
+        <v>10050</v>
+      </c>
+      <c r="D35" s="14"/>
+      <c r="E35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36">
+        <f>SUMIFS(G$3:G$22,J$3:J$22,K$35)</f>
+        <v>3590</v>
+      </c>
+      <c r="M36">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$35)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K37" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37">
+        <f>-SUMIFS(H$3:H$22,J$3:J$22,K$35)</f>
+        <v>-90</v>
+      </c>
+      <c r="M37">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$35)-COUNT(J$3:J$20,K$35,M$3:M$22)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K39" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K40" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L41" s="9">
+        <f>SUBTOTAL(9,L36:L40)</f>
+        <v>3500</v>
+      </c>
+      <c r="M41" s="9">
+        <f>M36</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K44" t="s">
+        <v>25</v>
+      </c>
+      <c r="L44">
+        <f>SUMIFS(G$3:G$22,J$3:J$22,K$43)</f>
+        <v>3370</v>
+      </c>
+      <c r="M44">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$43)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="11">
-        <f>C28+C29+C30</f>
-        <v>9690</v>
-      </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K33" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33">
-        <f>SUMIFS(G$3:G$20,J$3:J$20,K$32)</f>
-        <v>3590</v>
-      </c>
-      <c r="M33">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$32)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K34" t="s">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K45" t="s">
         <v>26</v>
       </c>
-      <c r="L34">
-        <f>-SUMIFS(H$3:H$20,J$3:J$20,K$32)+M34*5</f>
-        <v>-70</v>
-      </c>
-      <c r="M34">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$32)-COUNTIFS(J$3:J$20,K$32,M$3:M$20,"*gộp*")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K35" t="s">
+      <c r="L45">
+        <f>-SUMIFS(H$3:H$22,J$3:J$22,K$43)</f>
+        <v>-180</v>
+      </c>
+      <c r="M45">
+        <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$43)-COUNT(J$3:J$20,K$43,M$3:M$22)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K46" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="36" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K36" s="7" t="s">
+      <c r="L46">
+        <f>-M46*2</f>
+        <v>-38</v>
+      </c>
+      <c r="M46">
+        <f>Q23-(COUNTIFS(J$3:J$20,K$27,M$3:M$20,"*gộp*")/2)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K47" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K37" s="7" t="s">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K48" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L38" s="9">
-        <f>SUBTOTAL(9,L33:L37)</f>
-        <v>3520</v>
-      </c>
-      <c r="M38" s="9">
-        <f>M33</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K41" t="s">
-        <v>25</v>
-      </c>
-      <c r="L41">
-        <f>SUMIFS(G$3:G$20,J$3:J$20,K$40)</f>
-        <v>3370</v>
-      </c>
-      <c r="M41">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$40)</f>
+    <row r="49" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L49" s="9">
+        <f>SUBTOTAL(9,L44:L48)</f>
+        <v>3152</v>
+      </c>
+      <c r="M49" s="9">
+        <f>M44</f>
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K42" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42">
-        <f>-SUMIFS(H$3:H$20,J$3:J$20,K$40)+M42*5</f>
-        <v>-145</v>
-      </c>
-      <c r="M42">
-        <f>SUMIFS(Q$3:Q$20,J$3:J$20,K$40)-COUNTIFS(J$3:J$20,K$40,M$3:M$20,"*gộp*")</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K43" t="s">
-        <v>28</v>
-      </c>
-      <c r="L43">
-        <f>-M43*2</f>
-        <v>-34</v>
-      </c>
-      <c r="M43">
-        <f>Q22-(COUNTIFS(J$3:J$20,K$24,M$3:M$20,"*gộp*")/2)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K44" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="45" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="K45" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="11:13" x14ac:dyDescent="0.25">
-      <c r="L46" s="9">
-        <f>SUBTOTAL(9,L41:L45)</f>
-        <v>3191</v>
-      </c>
-      <c r="M46" s="9">
-        <f>M41</f>
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:Q2" xr:uid="{21EF95A6-1E82-4AC8-A681-DBF8AEA4F795}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:Q24">
-      <sortCondition ref="J2"/>
-    </sortState>
-  </autoFilter>
   <mergeCells count="8">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C31:D31"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/Mar/18-03-2026/NGAY 18-3.xlsx
+++ b/data/Mar/18-03-2026/NGAY 18-3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\TextExtractorTool\data\Mar\18-03-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\18-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE95C9FA-7173-46C8-A778-D9628FA1BB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398C755C-0066-46F1-85A2-62E6A142B5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EAF8504-9B99-4CC8-A026-1F30ACB00849}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="113">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -420,7 +420,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -452,6 +452,12 @@
         <fgColor rgb="FFADD8E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -476,15 +482,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -983,9 +989,6 @@
       <c r="L3" t="s">
         <v>48</v>
       </c>
-      <c r="M3" t="s">
-        <v>49</v>
-      </c>
       <c r="Q3">
         <v>1</v>
       </c>
@@ -1025,7 +1028,7 @@
       <c r="L4" t="s">
         <v>48</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="12" t="s">
         <v>49</v>
       </c>
       <c r="Q4">
@@ -1701,50 +1704,51 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+    <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="11">
         <v>750</v>
       </c>
-      <c r="H22" s="18">
-        <v>30</v>
-      </c>
-      <c r="I22" s="18">
-        <v>720</v>
-      </c>
-      <c r="J22" s="17" t="s">
+      <c r="H22" s="11">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <f>G22-H22</f>
+        <v>750</v>
+      </c>
+      <c r="J22" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="K22" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="17" t="s">
+      <c r="K22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="O22" s="17" t="s">
+      <c r="O22" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="P22" s="17" t="s">
+      <c r="P22" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1753,47 +1757,47 @@
         <f>COUNTA(D3:D20)</f>
         <v>14</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="6">
         <f>SUBTOTAL(9,G3:G22)</f>
         <v>12745</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="6">
         <f>SUBTOTAL(9,H3:H22)</f>
-        <v>505</v>
-      </c>
-      <c r="I23" s="15">
+        <v>475</v>
+      </c>
+      <c r="I23" s="6">
         <f>SUBTOTAL(9,I3:I22)</f>
-        <v>12240</v>
+        <v>12270</v>
       </c>
       <c r="J23" s="3">
-        <f>SUBTOTAL(9,J3:J20)</f>
+        <f t="shared" ref="J23:P23" si="0">SUBTOTAL(9,J3:J20)</f>
         <v>0</v>
       </c>
       <c r="K23" s="3">
-        <f>SUBTOTAL(9,K3:K20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L23" s="3">
-        <f>SUBTOTAL(9,L3:L20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M23" s="3">
-        <f>SUBTOTAL(9,M3:M20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N23" s="3">
-        <f>SUBTOTAL(9,N3:N20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O23" s="3">
-        <f>SUBTOTAL(9,O3:O20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <f>SUBTOTAL(9,P3:P20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="6">
         <f>SUBTOTAL(9,Q3:Q22)</f>
         <v>20</v>
       </c>
@@ -1803,12 +1807,6 @@
         <f>-3*17</f>
         <v>-51</v>
       </c>
-      <c r="I24">
-        <v>-750</v>
-      </c>
-      <c r="J24" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H25">
@@ -1820,10 +1818,10 @@
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="15"/>
       <c r="E27" s="4" t="s">
         <v>20</v>
       </c>
@@ -1848,10 +1846,10 @@
         <v>23</v>
       </c>
       <c r="C28" s="16">
-        <f>SUMIFS(I$3:I$22,B$3:B$22,A$27,L$3:L$22,A$28)+I24</f>
-        <v>10770</v>
-      </c>
-      <c r="D28" s="11"/>
+        <f>SUMIFS(I$3:I$22,B$3:B$22,A$27,L$3:L$22,A$28)</f>
+        <v>11520</v>
+      </c>
+      <c r="D28" s="17"/>
       <c r="E28" s="6">
         <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,L$3:L$22,A$28)</f>
         <v>19</v>
@@ -1882,10 +1880,10 @@
       <c r="B29" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="18">
         <v>0</v>
       </c>
-      <c r="D29" s="12"/>
+      <c r="D29" s="18"/>
       <c r="K29" t="s">
         <v>26</v>
       </c>
@@ -1902,7 +1900,7 @@
       </c>
       <c r="P29">
         <f>L41</f>
-        <v>3500</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -1911,10 +1909,10 @@
       </c>
       <c r="C30" s="19">
         <f>-SUMIFS(I$3:I$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
-        <v>-720</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="17">
+        <v>-750</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="10">
         <f>SUMIFS(Q$3:Q$22,B$3:B$22,A$27,P$3:P$22,"xx",N$3:N$22,"x")</f>
         <v>1</v>
       </c>
@@ -1926,18 +1924,18 @@
       </c>
       <c r="P30">
         <f>L49</f>
-        <v>3152</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="15">
         <f>SUBTOTAL(9,C28:C30)</f>
-        <v>10050</v>
-      </c>
-      <c r="D31" s="10"/>
+        <v>10770</v>
+      </c>
+      <c r="D31" s="15"/>
       <c r="E31">
         <f>E28</f>
         <v>19</v>
@@ -1950,7 +1948,7 @@
       </c>
       <c r="P31">
         <f>-C35</f>
-        <v>-10050</v>
+        <v>-10770</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -1970,7 +1968,7 @@
       </c>
       <c r="P32" s="4">
         <f>SUBTOTAL(9,P28:P31)</f>
-        <v>736</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
@@ -1994,7 +1992,7 @@
       </c>
       <c r="C35" s="14">
         <f>C31+C32+C33</f>
-        <v>10050</v>
+        <v>10770</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="3" t="s">
@@ -2028,8 +2026,7 @@
         <v>26</v>
       </c>
       <c r="L37">
-        <f>-SUMIFS(H$3:H$22,J$3:J$22,K$35)</f>
-        <v>-90</v>
+        <v>-70</v>
       </c>
       <c r="M37">
         <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$35)-COUNT(J$3:J$20,K$35,M$3:M$22)</f>
@@ -2054,7 +2051,7 @@
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L41" s="9">
         <f>SUBTOTAL(9,L36:L40)</f>
-        <v>3500</v>
+        <v>3520</v>
       </c>
       <c r="M41" s="9">
         <f>M36</f>
@@ -2090,8 +2087,7 @@
         <v>26</v>
       </c>
       <c r="L45">
-        <f>-SUMIFS(H$3:H$22,J$3:J$22,K$43)</f>
-        <v>-180</v>
+        <v>-145</v>
       </c>
       <c r="M45">
         <f>SUMIFS(Q$3:Q$22,J$3:J$22,K$43)-COUNT(J$3:J$20,K$43,M$3:M$22)</f>
@@ -2104,11 +2100,11 @@
       </c>
       <c r="L46">
         <f>-M46*2</f>
-        <v>-38</v>
+        <v>-37</v>
       </c>
       <c r="M46">
-        <f>Q23-(COUNTIFS(J$3:J$20,K$27,M$3:M$20,"*gộp*")/2)</f>
-        <v>19</v>
+        <f>E28-(COUNTIFS(J$3:J$22,K$27,M$3:M$22,"*gộp*")/2)</f>
+        <v>18.5</v>
       </c>
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.25">
@@ -2124,7 +2120,7 @@
     <row r="49" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L49" s="9">
         <f>SUBTOTAL(9,L44:L48)</f>
-        <v>3152</v>
+        <v>3188</v>
       </c>
       <c r="M49" s="9">
         <f>M44</f>
